--- a/港岛-北角-柏蔚山/柏蔚山_销控明细表.xlsx
+++ b/港岛-北角-柏蔚山/柏蔚山_销控明细表.xlsx
@@ -15096,7 +15096,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -38818,10 +38818,47 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 899呎 (3房)
+$2809万
+$31,244/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 615呎 (2房)
+$2371万
+$38,551/呎
+(19年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 617呎 (2房)
+$2265万
+$36,707/呎
+(19年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33&amp;35</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 3136呎 (4+房)
 $17716万
@@ -38829,7 +38866,7 @@
 (21年-03月-23日)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 2334呎 (4+房)
 $8578万
@@ -38837,7 +38874,7 @@
 (25年-12月-01日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 2375呎 (4+房)
 $11875万
@@ -38845,48 +38882,11 @@
 (19年-11月-20日)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
       <c r="E7" s="20" t="inlineStr"/>
       <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 899呎 (3房)
-$2809万
-$31,244/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 615呎 (2房)
-$2371万
-$38,551/呎
-(19年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>H | 617呎 (2房)
-$2265万
-$36,707/呎
-(19年-07月-09日)</t>
-        </is>
-      </c>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -40873,10 +40873,46 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1014呎 (4+房)
+$4398万
+$43,370/呎
+(19年-10月-22日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 1048呎 (4+房)
+$4284万
+$40,874/呎
+(20年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 1075呎 (4+房)
+$3477万
+$32,347/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33&amp;35</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2058呎 (4+房)
 $10496万
@@ -40884,8 +40920,8 @@
 (20年-04月-01日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1856呎 (4+房)
 $9317万
@@ -40893,8 +40929,8 @@
 (22年-07月-21日)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 2028呎 (4+房)
 $10500万
@@ -40902,44 +40938,8 @@
 (21年-03月-10日)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1014呎 (4+房)
-$4398万
-$43,370/呎
-(19年-10月-22日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 1048呎 (4+房)
-$4284万
-$40,874/呎
-(20年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 1075呎 (4+房)
-$3477万
-$32,347/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -41010,7 +41010,7 @@
           <t>A | 1271呎 (4+房)
 $3694万
 $29,066/呎
-(26年-08月-12日)</t>
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -42748,10 +42748,54 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 662呎 (1房)
+$2895万
+$43,731/呎
+(19年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 908呎 (3房)
+$2902万
+$31,961/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 908呎 (3房)
+$2840万
+$31,278/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 834呎 (3房)
+$2659万
+$31,880/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33&amp;35</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2503呎 (4+房)
 $12510万
@@ -42759,8 +42803,8 @@
 (23年-05月-22日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1624呎 (4+房)
 $8206万
@@ -42768,7 +42812,7 @@
 (20年-03月-23日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 2282呎 (4+房)
 $11684万
@@ -42776,54 +42820,10 @@
 (20年-04月-22日)</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 662呎 (1房)
-$2895万
-$43,731/呎
-(19年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
       <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 908呎 (3房)
-$2902万
-$31,961/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 908呎 (3房)
-$2840万
-$31,278/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>H | 834呎 (3房)
-$2659万
-$31,880/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">

--- a/港岛-北角-柏蔚山/柏蔚山_销控明细表.xlsx
+++ b/港岛-北角-柏蔚山/柏蔚山_销控明细表.xlsx
@@ -25879,30 +25879,38 @@
       </c>
       <c r="F408" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2020-04-22</t>
-        </is>
-      </c>
-      <c r="H408" s="5" t="n">
-        <v>116838400</v>
-      </c>
-      <c r="I408" s="5" t="n">
-        <v>51200</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H408" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I408" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J408" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K408" s="5" t="n">
-        <v>116838400</v>
-      </c>
-      <c r="L408" s="5" t="n">
-        <v>51200</v>
+      <c r="K408" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L408" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M408" s="3" t="inlineStr">
         <is>
@@ -25911,7 +25919,7 @@
       </c>
       <c r="N408" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38818,15 +38826,52 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
+          <t>33&amp;35</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 3136呎 (4+房)
+$17716万
+$56,491/呎
+(21年-03月-23日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2334呎 (4+房)
+$8578万
+$36,752/呎
+(25年-12月-01日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 2375呎 (4+房)
+$11875万
+$50,000/呎
+(19年-11月-20日)</t>
+        </is>
+      </c>
       <c r="E6" s="20" t="inlineStr"/>
       <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 899呎 (3房)
 $2809万
@@ -38834,7 +38879,7 @@
 (18年-07月-03日)</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 615呎 (2房)
 $2371万
@@ -38842,7 +38887,7 @@
 (19年-05月-27日)</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
 $2265万
@@ -38850,43 +38895,6 @@
 (19年-07月-09日)</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33&amp;35</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 3136呎 (4+房)
-$17716万
-$56,491/呎
-(21年-03月-23日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 2334呎 (4+房)
-$8578万
-$36,752/呎
-(25年-12月-01日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 2375呎 (4+房)
-$11875万
-$50,000/呎
-(19年-11月-20日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -40873,11 +40881,47 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33&amp;35</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2058呎 (4+房)
+$10496万
+$51,000/呎
+(20年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1856呎 (4+房)
+$9317万
+$50,200/呎
+(22年-07月-21日)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 2028呎 (4+房)
+$10500万
+$51,774/呎
+(21年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1014呎 (4+房)
 $4398万
@@ -40885,10 +40929,10 @@
 (19年-10月-22日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 1048呎 (4+房)
 $4284万
@@ -40896,7 +40940,7 @@
 (20年-09月-29日)</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 1075呎 (4+房)
 $3477万
@@ -40904,42 +40948,6 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33&amp;35</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2058呎 (4+房)
-$10496万
-$51,000/呎
-(20年-04月-01日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1856呎 (4+房)
-$9317万
-$50,200/呎
-(22年-07月-21日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>E | 2028呎 (4+房)
-$10500万
-$51,774/呎
-(21年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -42625,17 +42633,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>212</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -42748,11 +42756,48 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33&amp;35</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2503呎 (4+房)
+$12510万
+$49,980/呎
+(23年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1624呎 (4+房)
+$8206万
+$50,531/呎
+(20年-03月-23日)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 2282呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 662呎 (1房)
 $2895万
@@ -42760,10 +42805,10 @@
 (19年-05月-27日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 908呎 (3房)
 $2902万
@@ -42771,7 +42816,7 @@
 (18年-07月-03日)</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
 $2840万
@@ -42779,7 +42824,7 @@
 (18年-07月-03日)</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>H | 834呎 (3房)
 $2659万
@@ -42787,43 +42832,6 @@
 (18年-07月-03日)</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33&amp;35</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2503呎 (4+房)
-$12510万
-$49,980/呎
-(23年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1624呎 (4+房)
-$8206万
-$50,531/呎
-(20年-03月-23日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 2282呎 (4+房)
-$11684万
-$51,200/呎
-(20年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">

--- a/港岛-北角-柏蔚山/柏蔚山_销控明细表.xlsx
+++ b/港岛-北角-柏蔚山/柏蔚山_销控明细表.xlsx
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>25131000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>40863</v>
+        <v>40930</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>25131000</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>40863</v>
+        <v>40930</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>23709000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>38551</v>
+        <v>38614</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>23709000</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>38551</v>
+        <v>38614</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2334</v>
+        <v>2331</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>85780000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>36752</v>
+        <v>36800</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>85780000</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>36752</v>
+        <v>36800</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3136</v>
+        <v>3221</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>177155000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>56491</v>
+        <v>55000</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>177155000</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>56491</v>
+        <v>55000</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>22797000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>37068</v>
+        <v>37129</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>22797000</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>37068</v>
+        <v>37129</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>50581000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>42116</v>
+        <v>42081</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>50581000</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>42116</v>
+        <v>42081</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>66867000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>45028</v>
+        <v>44968</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>66867000</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>45028</v>
+        <v>44968</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>21593000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>35111</v>
+        <v>35168</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>21593000</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>35111</v>
+        <v>35168</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>48173000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>40111</v>
+        <v>40077</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>48173000</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>40111</v>
+        <v>40077</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>62730000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>42242</v>
+        <v>42186</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>62730000</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>42242</v>
+        <v>42186</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>58702000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>39530</v>
+        <v>39477</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>58702000</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>39530</v>
+        <v>39477</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>39543000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>32925</v>
+        <v>32898</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>39543000</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>32925</v>
+        <v>32898</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>51045000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>34374</v>
+        <v>34328</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>51045000</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>34374</v>
+        <v>34328</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>20755000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>33748</v>
+        <v>33803</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>20755000</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>33748</v>
+        <v>33803</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>39543000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>32925</v>
+        <v>32898</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>39543000</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>32925</v>
+        <v>32898</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>20033000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>32574</v>
+        <v>32627</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>20033000</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>32574</v>
+        <v>32627</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>39327000</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>32745</v>
+        <v>32718</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>39327000</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>32745</v>
+        <v>32718</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>19640000</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>31935</v>
+        <v>31987</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>19640000</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>31935</v>
+        <v>31987</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>48120000</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>32404</v>
+        <v>32360</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>48120000</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>32404</v>
+        <v>32360</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>21406000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>27408</v>
+        <v>27338</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>21406000</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>27408</v>
+        <v>27338</v>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>20576000</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>26346</v>
+        <v>26278</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>20576000</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>26346</v>
+        <v>26278</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>20373000</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>26086</v>
+        <v>26019</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>20373000</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>26086</v>
+        <v>26019</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>20172000</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>25828</v>
+        <v>25762</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>20172000</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>25828</v>
+        <v>25762</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="E120" s="4" t="n">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>20172000</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>25828</v>
+        <v>25762</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>20172000</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>25828</v>
+        <v>25762</v>
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="E129" s="4" t="n">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>19776000</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>25321</v>
+        <v>25257</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>19776000</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>25321</v>
+        <v>25257</v>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>23251000</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>29771</v>
+        <v>29695</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>23251000</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>29771</v>
+        <v>29695</v>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>20185000</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>25845</v>
+        <v>25779</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>20185000</v>
       </c>
       <c r="L147" s="5" t="n">
-        <v>25845</v>
+        <v>25779</v>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         </is>
       </c>
       <c r="E165" s="4" t="n">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>19985000</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>25589</v>
+        <v>25524</v>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>19985000</v>
       </c>
       <c r="L165" s="5" t="n">
-        <v>25589</v>
+        <v>25524</v>
       </c>
       <c r="M165" s="3" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>23615000</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>30237</v>
+        <v>30160</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>23615000</v>
       </c>
       <c r="L174" s="5" t="n">
-        <v>30237</v>
+        <v>30160</v>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="E183" s="4" t="n">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>19787000</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>25335</v>
+        <v>25271</v>
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>19787000</v>
       </c>
       <c r="L183" s="5" t="n">
-        <v>25335</v>
+        <v>25271</v>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         </is>
       </c>
       <c r="E192" s="4" t="n">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>19688000</v>
       </c>
       <c r="I192" s="5" t="n">
-        <v>25209</v>
+        <v>25144</v>
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>19688000</v>
       </c>
       <c r="L192" s="5" t="n">
-        <v>25209</v>
+        <v>25144</v>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="E201" s="4" t="n">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>19591000</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>25085</v>
+        <v>25020</v>
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>19591000</v>
       </c>
       <c r="L201" s="5" t="n">
-        <v>25085</v>
+        <v>25020</v>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         </is>
       </c>
       <c r="E219" s="4" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>104998600</v>
       </c>
       <c r="I219" s="5" t="n">
-        <v>51774</v>
+        <v>51800</v>
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>104998600</v>
       </c>
       <c r="L219" s="5" t="n">
-        <v>51774</v>
+        <v>51800</v>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         </is>
       </c>
       <c r="E224" s="4" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>42946000</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>41614</v>
+        <v>41574</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>42946000</v>
       </c>
       <c r="L224" s="5" t="n">
-        <v>41614</v>
+        <v>41574</v>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="E230" s="4" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>41695000</v>
       </c>
       <c r="I230" s="5" t="n">
-        <v>40402</v>
+        <v>40363</v>
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>41695000</v>
       </c>
       <c r="L230" s="5" t="n">
-        <v>40402</v>
+        <v>40363</v>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         </is>
       </c>
       <c r="E248" s="4" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>28208000</v>
       </c>
       <c r="I248" s="5" t="n">
-        <v>27333</v>
+        <v>27307</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>28208000</v>
       </c>
       <c r="L248" s="5" t="n">
-        <v>27333</v>
+        <v>27307</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         </is>
       </c>
       <c r="E254" s="4" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>27654000</v>
       </c>
       <c r="I254" s="5" t="n">
-        <v>26797</v>
+        <v>26771</v>
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>27654000</v>
       </c>
       <c r="L254" s="5" t="n">
-        <v>26797</v>
+        <v>26771</v>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         </is>
       </c>
       <c r="E260" s="4" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>37691000</v>
       </c>
       <c r="I260" s="5" t="n">
-        <v>36522</v>
+        <v>36487</v>
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>37691000</v>
       </c>
       <c r="L260" s="5" t="n">
-        <v>36522</v>
+        <v>36487</v>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         </is>
       </c>
       <c r="E266" s="4" t="n">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>27265000</v>
       </c>
       <c r="I266" s="5" t="n">
-        <v>30028</v>
+        <v>29994</v>
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>27265000</v>
       </c>
       <c r="L266" s="5" t="n">
-        <v>30028</v>
+        <v>29994</v>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         </is>
       </c>
       <c r="E267" s="4" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>24468000</v>
       </c>
       <c r="I267" s="5" t="n">
-        <v>29233</v>
+        <v>29198</v>
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>24468000</v>
       </c>
       <c r="L267" s="5" t="n">
-        <v>29233</v>
+        <v>29198</v>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         </is>
       </c>
       <c r="E268" s="4" t="n">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>20991000</v>
       </c>
       <c r="I268" s="5" t="n">
-        <v>31006</v>
+        <v>30960</v>
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>20991000</v>
       </c>
       <c r="L268" s="5" t="n">
-        <v>31006</v>
+        <v>30960</v>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         </is>
       </c>
       <c r="E272" s="4" t="n">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
@@ -17459,7 +17459,7 @@
         <v>27300000</v>
       </c>
       <c r="I272" s="5" t="n">
-        <v>33913</v>
+        <v>33955</v>
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>27300000</v>
       </c>
       <c r="L272" s="5" t="n">
-        <v>33913</v>
+        <v>33955</v>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         </is>
       </c>
       <c r="E274" s="4" t="n">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>26862000</v>
       </c>
       <c r="I274" s="5" t="n">
-        <v>29584</v>
+        <v>29551</v>
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>26862000</v>
       </c>
       <c r="L274" s="5" t="n">
-        <v>29584</v>
+        <v>29551</v>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         </is>
       </c>
       <c r="E275" s="4" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>24107000</v>
       </c>
       <c r="I275" s="5" t="n">
-        <v>28802</v>
+        <v>28767</v>
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>24107000</v>
       </c>
       <c r="L275" s="5" t="n">
-        <v>28802</v>
+        <v>28767</v>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         </is>
       </c>
       <c r="E280" s="4" t="n">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>26505000</v>
       </c>
       <c r="I280" s="5" t="n">
-        <v>32925</v>
+        <v>32966</v>
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>26505000</v>
       </c>
       <c r="L280" s="5" t="n">
-        <v>32925</v>
+        <v>32966</v>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         </is>
       </c>
       <c r="E282" s="4" t="n">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>26465000</v>
       </c>
       <c r="I282" s="5" t="n">
-        <v>29146</v>
+        <v>29114</v>
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>26465000</v>
       </c>
       <c r="L282" s="5" t="n">
-        <v>29146</v>
+        <v>29114</v>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         </is>
       </c>
       <c r="E288" s="4" t="n">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>25733000</v>
       </c>
       <c r="I288" s="5" t="n">
-        <v>31966</v>
+        <v>32006</v>
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>25733000</v>
       </c>
       <c r="L288" s="5" t="n">
-        <v>31966</v>
+        <v>32006</v>
       </c>
       <c r="M288" s="3" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="E296" s="4" t="n">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>25478000</v>
       </c>
       <c r="I296" s="5" t="n">
-        <v>31650</v>
+        <v>31689</v>
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>25478000</v>
       </c>
       <c r="L296" s="5" t="n">
-        <v>31650</v>
+        <v>31689</v>
       </c>
       <c r="M296" s="3" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="E299" s="4" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>23053000</v>
       </c>
       <c r="I299" s="5" t="n">
-        <v>27542</v>
+        <v>27510</v>
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>23053000</v>
       </c>
       <c r="L299" s="5" t="n">
-        <v>27542</v>
+        <v>27510</v>
       </c>
       <c r="M299" s="3" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         </is>
       </c>
       <c r="E306" s="4" t="n">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>25561000</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>28151</v>
+        <v>28120</v>
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>25561000</v>
       </c>
       <c r="L306" s="5" t="n">
-        <v>28151</v>
+        <v>28120</v>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         </is>
       </c>
       <c r="E314" s="4" t="n">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F314" s="3" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>25561000</v>
       </c>
       <c r="I314" s="5" t="n">
-        <v>28151</v>
+        <v>28120</v>
       </c>
       <c r="J314" s="3" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>25561000</v>
       </c>
       <c r="L314" s="5" t="n">
-        <v>28151</v>
+        <v>28120</v>
       </c>
       <c r="M314" s="3" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         </is>
       </c>
       <c r="E316" s="4" t="n">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F316" s="3" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>18836000</v>
       </c>
       <c r="I316" s="5" t="n">
-        <v>27823</v>
+        <v>27782</v>
       </c>
       <c r="J316" s="3" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>18836000</v>
       </c>
       <c r="L316" s="5" t="n">
-        <v>27823</v>
+        <v>27782</v>
       </c>
       <c r="M316" s="3" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         </is>
       </c>
       <c r="E322" s="4" t="n">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>25308000</v>
       </c>
       <c r="I322" s="5" t="n">
-        <v>27872</v>
+        <v>27842</v>
       </c>
       <c r="J322" s="3" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>25308000</v>
       </c>
       <c r="L322" s="5" t="n">
-        <v>27872</v>
+        <v>27842</v>
       </c>
       <c r="M322" s="3" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         </is>
       </c>
       <c r="E324" s="4" t="n">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F324" s="3" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>18467000</v>
       </c>
       <c r="I324" s="5" t="n">
-        <v>27278</v>
+        <v>27237</v>
       </c>
       <c r="J324" s="3" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>18467000</v>
       </c>
       <c r="L324" s="5" t="n">
-        <v>27278</v>
+        <v>27237</v>
       </c>
       <c r="M324" s="3" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         </is>
       </c>
       <c r="E328" s="4" t="n">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F328" s="3" t="inlineStr">
         <is>
@@ -20931,7 +20931,7 @@
         <v>24487000</v>
       </c>
       <c r="I328" s="5" t="n">
-        <v>30419</v>
+        <v>30456</v>
       </c>
       <c r="J328" s="3" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>24487000</v>
       </c>
       <c r="L328" s="5" t="n">
-        <v>30419</v>
+        <v>30456</v>
       </c>
       <c r="M328" s="3" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         </is>
       </c>
       <c r="E336" s="4" t="n">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F336" s="3" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>24244000</v>
       </c>
       <c r="I336" s="5" t="n">
-        <v>30117</v>
+        <v>30154</v>
       </c>
       <c r="J336" s="3" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>24244000</v>
       </c>
       <c r="L336" s="5" t="n">
-        <v>30117</v>
+        <v>30154</v>
       </c>
       <c r="M336" s="3" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         </is>
       </c>
       <c r="E338" s="4" t="n">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F338" s="3" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>25056000</v>
       </c>
       <c r="I338" s="5" t="n">
-        <v>27595</v>
+        <v>27564</v>
       </c>
       <c r="J338" s="3" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>25056000</v>
       </c>
       <c r="L338" s="5" t="n">
-        <v>27595</v>
+        <v>27564</v>
       </c>
       <c r="M338" s="3" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         </is>
       </c>
       <c r="E347" s="4" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F347" s="3" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>22375000</v>
       </c>
       <c r="I347" s="5" t="n">
-        <v>26732</v>
+        <v>26700</v>
       </c>
       <c r="J347" s="3" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>22375000</v>
       </c>
       <c r="L347" s="5" t="n">
-        <v>26732</v>
+        <v>26700</v>
       </c>
       <c r="M347" s="3" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         </is>
       </c>
       <c r="E348" s="4" t="n">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F348" s="3" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>18103000</v>
       </c>
       <c r="I348" s="5" t="n">
-        <v>26740</v>
+        <v>26701</v>
       </c>
       <c r="J348" s="3" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>18103000</v>
       </c>
       <c r="L348" s="5" t="n">
-        <v>26740</v>
+        <v>26701</v>
       </c>
       <c r="M348" s="3" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         </is>
       </c>
       <c r="E352" s="4" t="n">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F352" s="3" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>23767000</v>
       </c>
       <c r="I352" s="5" t="n">
-        <v>29524</v>
+        <v>29561</v>
       </c>
       <c r="J352" s="3" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>23767000</v>
       </c>
       <c r="L352" s="5" t="n">
-        <v>29524</v>
+        <v>29561</v>
       </c>
       <c r="M352" s="3" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="E356" s="4" t="n">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>18012000</v>
       </c>
       <c r="I356" s="5" t="n">
-        <v>26606</v>
+        <v>26566</v>
       </c>
       <c r="J356" s="3" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>18012000</v>
       </c>
       <c r="L356" s="5" t="n">
-        <v>26606</v>
+        <v>26566</v>
       </c>
       <c r="M356" s="3" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         </is>
       </c>
       <c r="E362" s="4" t="n">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>24684000</v>
       </c>
       <c r="I362" s="5" t="n">
-        <v>27185</v>
+        <v>27155</v>
       </c>
       <c r="J362" s="3" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>24684000</v>
       </c>
       <c r="L362" s="5" t="n">
-        <v>27185</v>
+        <v>27155</v>
       </c>
       <c r="M362" s="3" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         </is>
       </c>
       <c r="E364" s="4" t="n">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>17923000</v>
       </c>
       <c r="I364" s="5" t="n">
-        <v>26474</v>
+        <v>26435</v>
       </c>
       <c r="J364" s="3" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>17923000</v>
       </c>
       <c r="L364" s="5" t="n">
-        <v>26474</v>
+        <v>26435</v>
       </c>
       <c r="M364" s="3" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         </is>
       </c>
       <c r="E376" s="4" t="n">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F376" s="3" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>22730000</v>
       </c>
       <c r="I376" s="5" t="n">
-        <v>28236</v>
+        <v>28271</v>
       </c>
       <c r="J376" s="3" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>22730000</v>
       </c>
       <c r="L376" s="5" t="n">
-        <v>28236</v>
+        <v>28271</v>
       </c>
       <c r="M376" s="3" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         </is>
       </c>
       <c r="E379" s="4" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F379" s="3" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>22097000</v>
       </c>
       <c r="I379" s="5" t="n">
-        <v>26400</v>
+        <v>26369</v>
       </c>
       <c r="J379" s="3" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>22097000</v>
       </c>
       <c r="L379" s="5" t="n">
-        <v>26400</v>
+        <v>26369</v>
       </c>
       <c r="M379" s="3" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         </is>
       </c>
       <c r="E380" s="4" t="n">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>17878000</v>
       </c>
       <c r="I380" s="5" t="n">
-        <v>26408</v>
+        <v>26369</v>
       </c>
       <c r="J380" s="3" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>17878000</v>
       </c>
       <c r="L380" s="5" t="n">
-        <v>26408</v>
+        <v>26369</v>
       </c>
       <c r="M380" s="3" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         </is>
       </c>
       <c r="E384" s="4" t="n">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>22730000</v>
       </c>
       <c r="I384" s="5" t="n">
-        <v>28236</v>
+        <v>28271</v>
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>22730000</v>
       </c>
       <c r="L384" s="5" t="n">
-        <v>28236</v>
+        <v>28271</v>
       </c>
       <c r="M384" s="3" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         </is>
       </c>
       <c r="E386" s="4" t="n">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>24500000</v>
       </c>
       <c r="I386" s="5" t="n">
-        <v>26982</v>
+        <v>26953</v>
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
@@ -24538,7 +24538,7 @@
         <v>24500000</v>
       </c>
       <c r="L386" s="5" t="n">
-        <v>26982</v>
+        <v>26953</v>
       </c>
       <c r="M386" s="3" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         </is>
       </c>
       <c r="E387" s="4" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F387" s="3" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>21987000</v>
       </c>
       <c r="I387" s="5" t="n">
-        <v>26269</v>
+        <v>26237</v>
       </c>
       <c r="J387" s="3" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>21987000</v>
       </c>
       <c r="L387" s="5" t="n">
-        <v>26269</v>
+        <v>26237</v>
       </c>
       <c r="M387" s="3" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         </is>
       </c>
       <c r="E394" s="4" t="n">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F394" s="3" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>24440000</v>
       </c>
       <c r="I394" s="5" t="n">
-        <v>26916</v>
+        <v>26887</v>
       </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>24440000</v>
       </c>
       <c r="L394" s="5" t="n">
-        <v>26916</v>
+        <v>26887</v>
       </c>
       <c r="M394" s="3" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         </is>
       </c>
       <c r="E395" s="4" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F395" s="3" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>21932000</v>
       </c>
       <c r="I395" s="5" t="n">
-        <v>26203</v>
+        <v>26172</v>
       </c>
       <c r="J395" s="3" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>21932000</v>
       </c>
       <c r="L395" s="5" t="n">
-        <v>26203</v>
+        <v>26172</v>
       </c>
       <c r="M395" s="3" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         </is>
       </c>
       <c r="E396" s="4" t="n">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F396" s="3" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>17745000</v>
       </c>
       <c r="I396" s="5" t="n">
-        <v>26211</v>
+        <v>26173</v>
       </c>
       <c r="J396" s="3" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>17745000</v>
       </c>
       <c r="L396" s="5" t="n">
-        <v>26211</v>
+        <v>26173</v>
       </c>
       <c r="M396" s="3" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         </is>
       </c>
       <c r="E400" s="4" t="n">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F400" s="3" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>22393000</v>
       </c>
       <c r="I400" s="5" t="n">
-        <v>27817</v>
+        <v>27852</v>
       </c>
       <c r="J400" s="3" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>22393000</v>
       </c>
       <c r="L400" s="5" t="n">
-        <v>27817</v>
+        <v>27852</v>
       </c>
       <c r="M400" s="3" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         </is>
       </c>
       <c r="E402" s="4" t="n">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>28968000</v>
       </c>
       <c r="I402" s="5" t="n">
-        <v>31938</v>
+        <v>31903</v>
       </c>
       <c r="J402" s="3" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>28968000</v>
       </c>
       <c r="L402" s="5" t="n">
-        <v>31938</v>
+        <v>31903</v>
       </c>
       <c r="M402" s="3" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         </is>
       </c>
       <c r="E404" s="4" t="n">
-        <v>662</v>
+        <v>622</v>
       </c>
       <c r="F404" s="3" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>31061000</v>
       </c>
       <c r="I404" s="5" t="n">
-        <v>46920</v>
+        <v>49937</v>
       </c>
       <c r="J404" s="3" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>31061000</v>
       </c>
       <c r="L404" s="5" t="n">
-        <v>46920</v>
+        <v>49937</v>
       </c>
       <c r="M404" s="3" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="E409" s="4" t="n">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="F409" s="3" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>82062500</v>
       </c>
       <c r="I409" s="5" t="n">
-        <v>50531</v>
+        <v>50500</v>
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>82062500</v>
       </c>
       <c r="L409" s="5" t="n">
-        <v>50531</v>
+        <v>50500</v>
       </c>
       <c r="M409" s="3" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         </is>
       </c>
       <c r="E411" s="4" t="n">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="F411" s="3" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>125100000</v>
       </c>
       <c r="I411" s="5" t="n">
-        <v>49980</v>
+        <v>50000</v>
       </c>
       <c r="J411" s="3" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>125100000</v>
       </c>
       <c r="L411" s="5" t="n">
-        <v>49980</v>
+        <v>50000</v>
       </c>
       <c r="M411" s="3" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         </is>
       </c>
       <c r="E414" s="4" t="n">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F414" s="3" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>26213000</v>
       </c>
       <c r="I414" s="5" t="n">
-        <v>29720</v>
+        <v>29754</v>
       </c>
       <c r="J414" s="3" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>26213000</v>
       </c>
       <c r="L414" s="5" t="n">
-        <v>29720</v>
+        <v>29754</v>
       </c>
       <c r="M414" s="3" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         </is>
       </c>
       <c r="E416" s="4" t="n">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="F416" s="3" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>31686000</v>
       </c>
       <c r="I416" s="5" t="n">
-        <v>39657</v>
+        <v>39707</v>
       </c>
       <c r="J416" s="3" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>31686000</v>
       </c>
       <c r="L416" s="5" t="n">
-        <v>39657</v>
+        <v>39707</v>
       </c>
       <c r="M416" s="3" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         </is>
       </c>
       <c r="E417" s="4" t="n">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F417" s="3" t="inlineStr">
         <is>
@@ -26457,7 +26457,7 @@
         <v>25861000</v>
       </c>
       <c r="I417" s="5" t="n">
-        <v>41982</v>
+        <v>42050</v>
       </c>
       <c r="J417" s="3" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>25861000</v>
       </c>
       <c r="L417" s="5" t="n">
-        <v>41982</v>
+        <v>42050</v>
       </c>
       <c r="M417" s="3" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         </is>
       </c>
       <c r="E418" s="4" t="n">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="F418" s="3" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>69384000</v>
       </c>
       <c r="I418" s="5" t="n">
-        <v>45919</v>
+        <v>45889</v>
       </c>
       <c r="J418" s="3" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>69384000</v>
       </c>
       <c r="L418" s="5" t="n">
-        <v>45919</v>
+        <v>45889</v>
       </c>
       <c r="M418" s="3" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         </is>
       </c>
       <c r="E421" s="4" t="n">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>25700000</v>
       </c>
       <c r="I421" s="5" t="n">
-        <v>29138</v>
+        <v>29171</v>
       </c>
       <c r="J421" s="3" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>25700000</v>
       </c>
       <c r="L421" s="5" t="n">
-        <v>29138</v>
+        <v>29171</v>
       </c>
       <c r="M421" s="3" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         </is>
       </c>
       <c r="E424" s="4" t="n">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F424" s="3" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>24028000</v>
       </c>
       <c r="I424" s="5" t="n">
-        <v>39006</v>
+        <v>39070</v>
       </c>
       <c r="J424" s="3" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>24028000</v>
       </c>
       <c r="L424" s="5" t="n">
-        <v>39006</v>
+        <v>39070</v>
       </c>
       <c r="M424" s="3" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         </is>
       </c>
       <c r="E425" s="4" t="n">
-        <v>1536</v>
+        <v>1512</v>
       </c>
       <c r="F425" s="3" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>66886000</v>
       </c>
       <c r="I425" s="5" t="n">
-        <v>43546</v>
+        <v>44237</v>
       </c>
       <c r="J425" s="3" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>66886000</v>
       </c>
       <c r="L425" s="5" t="n">
-        <v>43546</v>
+        <v>44237</v>
       </c>
       <c r="M425" s="3" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         </is>
       </c>
       <c r="E428" s="4" t="n">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F428" s="3" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>25196000</v>
       </c>
       <c r="I428" s="5" t="n">
-        <v>28567</v>
+        <v>28599</v>
       </c>
       <c r="J428" s="3" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         <v>25196000</v>
       </c>
       <c r="L428" s="5" t="n">
-        <v>28567</v>
+        <v>28599</v>
       </c>
       <c r="M428" s="3" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         </is>
       </c>
       <c r="E430" s="4" t="n">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="F430" s="3" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>27942000</v>
       </c>
       <c r="I430" s="5" t="n">
-        <v>34971</v>
+        <v>35015</v>
       </c>
       <c r="J430" s="3" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>27942000</v>
       </c>
       <c r="L430" s="5" t="n">
-        <v>34971</v>
+        <v>35015</v>
       </c>
       <c r="M430" s="3" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         </is>
       </c>
       <c r="E431" s="4" t="n">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F431" s="3" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>23328000</v>
       </c>
       <c r="I431" s="5" t="n">
-        <v>37870</v>
+        <v>37932</v>
       </c>
       <c r="J431" s="3" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>23328000</v>
       </c>
       <c r="L431" s="5" t="n">
-        <v>37870</v>
+        <v>37932</v>
       </c>
       <c r="M431" s="3" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         </is>
       </c>
       <c r="E435" s="4" t="n">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F435" s="3" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>24702000</v>
       </c>
       <c r="I435" s="5" t="n">
-        <v>28007</v>
+        <v>28039</v>
       </c>
       <c r="J435" s="3" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>24702000</v>
       </c>
       <c r="L435" s="5" t="n">
-        <v>28007</v>
+        <v>28039</v>
       </c>
       <c r="M435" s="3" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         </is>
       </c>
       <c r="E439" s="4" t="n">
-        <v>1536</v>
+        <v>1512</v>
       </c>
       <c r="F439" s="3" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>54960000</v>
       </c>
       <c r="I439" s="5" t="n">
-        <v>35781</v>
+        <v>36349</v>
       </c>
       <c r="J439" s="3" t="inlineStr">
         <is>
@@ -27832,7 +27832,7 @@
         <v>54960000</v>
       </c>
       <c r="L439" s="5" t="n">
-        <v>35781</v>
+        <v>36349</v>
       </c>
       <c r="M439" s="3" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         </is>
       </c>
       <c r="E441" s="4" t="n">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="F441" s="3" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>26238000</v>
       </c>
       <c r="I441" s="5" t="n">
-        <v>28928</v>
+        <v>28896</v>
       </c>
       <c r="J441" s="3" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>26238000</v>
       </c>
       <c r="L441" s="5" t="n">
-        <v>28928</v>
+        <v>28896</v>
       </c>
       <c r="M441" s="3" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         </is>
       </c>
       <c r="E445" s="4" t="n">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F445" s="3" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>22872000</v>
       </c>
       <c r="I445" s="5" t="n">
-        <v>37130</v>
+        <v>37190</v>
       </c>
       <c r="J445" s="3" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>22872000</v>
       </c>
       <c r="L445" s="5" t="n">
-        <v>37130</v>
+        <v>37190</v>
       </c>
       <c r="M445" s="3" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         </is>
       </c>
       <c r="E448" s="4" t="n">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="F448" s="3" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>25326000</v>
       </c>
       <c r="I448" s="5" t="n">
-        <v>27923</v>
+        <v>27892</v>
       </c>
       <c r="J448" s="3" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>25326000</v>
       </c>
       <c r="L448" s="5" t="n">
-        <v>27923</v>
+        <v>27892</v>
       </c>
       <c r="M448" s="3" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         </is>
       </c>
       <c r="E451" s="4" t="n">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="F451" s="3" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>27438000</v>
       </c>
       <c r="I451" s="5" t="n">
-        <v>34340</v>
+        <v>34383</v>
       </c>
       <c r="J451" s="3" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>27438000</v>
       </c>
       <c r="L451" s="5" t="n">
-        <v>34340</v>
+        <v>34383</v>
       </c>
       <c r="M451" s="3" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         </is>
       </c>
       <c r="E452" s="4" t="n">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F452" s="3" t="inlineStr">
         <is>
@@ -28627,7 +28627,7 @@
         <v>21992000</v>
       </c>
       <c r="I452" s="5" t="n">
-        <v>35701</v>
+        <v>35759</v>
       </c>
       <c r="J452" s="3" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>21992000</v>
       </c>
       <c r="L452" s="5" t="n">
-        <v>35701</v>
+        <v>35759</v>
       </c>
       <c r="M452" s="3" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         </is>
       </c>
       <c r="E453" s="4" t="n">
-        <v>1537</v>
+        <v>1512</v>
       </c>
       <c r="F453" s="3" t="inlineStr">
         <is>
@@ -28689,7 +28689,7 @@
         <v>57920000</v>
       </c>
       <c r="I453" s="5" t="n">
-        <v>37684</v>
+        <v>38307</v>
       </c>
       <c r="J453" s="3" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>57920000</v>
       </c>
       <c r="L453" s="5" t="n">
-        <v>37684</v>
+        <v>38307</v>
       </c>
       <c r="M453" s="3" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         </is>
       </c>
       <c r="E459" s="4" t="n">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F459" s="3" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>21560000</v>
       </c>
       <c r="I459" s="5" t="n">
-        <v>35000</v>
+        <v>35057</v>
       </c>
       <c r="J459" s="3" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>21560000</v>
       </c>
       <c r="L459" s="5" t="n">
-        <v>35000</v>
+        <v>35057</v>
       </c>
       <c r="M459" s="3" t="inlineStr">
         <is>
@@ -29107,7 +29107,7 @@
         </is>
       </c>
       <c r="E460" s="4" t="n">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="F460" s="3" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         <v>58203000</v>
       </c>
       <c r="I460" s="5" t="n">
-        <v>38520</v>
+        <v>38494</v>
       </c>
       <c r="J460" s="3" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>58203000</v>
       </c>
       <c r="L460" s="5" t="n">
-        <v>38520</v>
+        <v>38494</v>
       </c>
       <c r="M460" s="3" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         </is>
       </c>
       <c r="E469" s="4" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F469" s="3" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>19528000</v>
       </c>
       <c r="I469" s="5" t="n">
-        <v>29768</v>
+        <v>29814</v>
       </c>
       <c r="J469" s="3" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>19528000</v>
       </c>
       <c r="L469" s="5" t="n">
-        <v>29768</v>
+        <v>29814</v>
       </c>
       <c r="M469" s="3" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         </is>
       </c>
       <c r="E481" s="4" t="n">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F481" s="3" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>23707000</v>
       </c>
       <c r="I481" s="5" t="n">
-        <v>25995</v>
+        <v>26023</v>
       </c>
       <c r="J481" s="3" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>23707000</v>
       </c>
       <c r="L481" s="5" t="n">
-        <v>25995</v>
+        <v>26023</v>
       </c>
       <c r="M481" s="3" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         </is>
       </c>
       <c r="E487" s="4" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F487" s="3" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>18408000</v>
       </c>
       <c r="I487" s="5" t="n">
-        <v>28061</v>
+        <v>28104</v>
       </c>
       <c r="J487" s="3" t="inlineStr">
         <is>
@@ -30808,7 +30808,7 @@
         <v>18408000</v>
       </c>
       <c r="L487" s="5" t="n">
-        <v>28061</v>
+        <v>28104</v>
       </c>
       <c r="M487" s="3" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         </is>
       </c>
       <c r="E496" s="4" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F496" s="3" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>18225000</v>
       </c>
       <c r="I496" s="5" t="n">
-        <v>27782</v>
+        <v>27824</v>
       </c>
       <c r="J496" s="3" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>18225000</v>
       </c>
       <c r="L496" s="5" t="n">
-        <v>27782</v>
+        <v>27824</v>
       </c>
       <c r="M496" s="3" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         </is>
       </c>
       <c r="E499" s="4" t="n">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F499" s="3" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>23012000</v>
       </c>
       <c r="I499" s="5" t="n">
-        <v>25232</v>
+        <v>25260</v>
       </c>
       <c r="J499" s="3" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>23012000</v>
       </c>
       <c r="L499" s="5" t="n">
-        <v>25232</v>
+        <v>25260</v>
       </c>
       <c r="M499" s="3" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         </is>
       </c>
       <c r="E505" s="4" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F505" s="3" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>18045000</v>
       </c>
       <c r="I505" s="5" t="n">
-        <v>27508</v>
+        <v>27550</v>
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>18045000</v>
       </c>
       <c r="L505" s="5" t="n">
-        <v>27508</v>
+        <v>27550</v>
       </c>
       <c r="M505" s="3" t="inlineStr">
         <is>
@@ -32083,7 +32083,7 @@
         </is>
       </c>
       <c r="E508" s="4" t="n">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F508" s="3" t="inlineStr">
         <is>
@@ -32099,7 +32099,7 @@
         <v>24113000</v>
       </c>
       <c r="I508" s="5" t="n">
-        <v>26440</v>
+        <v>26469</v>
       </c>
       <c r="J508" s="3" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>24113000</v>
       </c>
       <c r="L508" s="5" t="n">
-        <v>26440</v>
+        <v>26469</v>
       </c>
       <c r="M508" s="3" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         </is>
       </c>
       <c r="E517" s="4" t="n">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F517" s="3" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>24113000</v>
       </c>
       <c r="I517" s="5" t="n">
-        <v>26440</v>
+        <v>26469</v>
       </c>
       <c r="J517" s="3" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>24113000</v>
       </c>
       <c r="L517" s="5" t="n">
-        <v>26440</v>
+        <v>26469</v>
       </c>
       <c r="M517" s="3" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         </is>
       </c>
       <c r="E526" s="4" t="n">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F526" s="3" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>22870000</v>
       </c>
       <c r="I526" s="5" t="n">
-        <v>25077</v>
+        <v>25104</v>
       </c>
       <c r="J526" s="3" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>22870000</v>
       </c>
       <c r="L526" s="5" t="n">
-        <v>25077</v>
+        <v>25104</v>
       </c>
       <c r="M526" s="3" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         </is>
       </c>
       <c r="E532" s="4" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F532" s="3" t="inlineStr">
         <is>
@@ -33587,7 +33587,7 @@
         <v>17516000</v>
       </c>
       <c r="I532" s="5" t="n">
-        <v>26701</v>
+        <v>26742</v>
       </c>
       <c r="J532" s="3" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>17516000</v>
       </c>
       <c r="L532" s="5" t="n">
-        <v>26701</v>
+        <v>26742</v>
       </c>
       <c r="M532" s="3" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         </is>
       </c>
       <c r="E535" s="4" t="n">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F535" s="3" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>24397000</v>
       </c>
       <c r="I535" s="5" t="n">
-        <v>26751</v>
+        <v>26780</v>
       </c>
       <c r="J535" s="3" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>24397000</v>
       </c>
       <c r="L535" s="5" t="n">
-        <v>26751</v>
+        <v>26780</v>
       </c>
       <c r="M535" s="3" t="inlineStr">
         <is>
@@ -34129,7 +34129,7 @@
         </is>
       </c>
       <c r="E541" s="4" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F541" s="3" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>17343000</v>
       </c>
       <c r="I541" s="5" t="n">
-        <v>26438</v>
+        <v>26478</v>
       </c>
       <c r="J541" s="3" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>17343000</v>
       </c>
       <c r="L541" s="5" t="n">
-        <v>26438</v>
+        <v>26478</v>
       </c>
       <c r="M541" s="3" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         </is>
       </c>
       <c r="E544" s="4" t="n">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F544" s="3" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>24519000</v>
       </c>
       <c r="I544" s="5" t="n">
-        <v>26885</v>
+        <v>26914</v>
       </c>
       <c r="J544" s="3" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>24519000</v>
       </c>
       <c r="L544" s="5" t="n">
-        <v>26885</v>
+        <v>26914</v>
       </c>
       <c r="M544" s="3" t="inlineStr">
         <is>
@@ -34873,7 +34873,7 @@
         </is>
       </c>
       <c r="E553" s="4" t="n">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F553" s="3" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>24396000</v>
       </c>
       <c r="I553" s="5" t="n">
-        <v>26750</v>
+        <v>26779</v>
       </c>
       <c r="J553" s="3" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>24396000</v>
       </c>
       <c r="L553" s="5" t="n">
-        <v>26750</v>
+        <v>26779</v>
       </c>
       <c r="M553" s="3" t="inlineStr">
         <is>
@@ -35803,7 +35803,7 @@
         </is>
       </c>
       <c r="E568" s="4" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F568" s="3" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>17085000</v>
       </c>
       <c r="I568" s="5" t="n">
-        <v>26044</v>
+        <v>26084</v>
       </c>
       <c r="J568" s="3" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>17085000</v>
       </c>
       <c r="L568" s="5" t="n">
-        <v>26044</v>
+        <v>26084</v>
       </c>
       <c r="M568" s="3" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         </is>
       </c>
       <c r="E571" s="4" t="n">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F571" s="3" t="inlineStr">
         <is>
@@ -36005,7 +36005,7 @@
         <v>24155000</v>
       </c>
       <c r="I571" s="5" t="n">
-        <v>26486</v>
+        <v>26515</v>
       </c>
       <c r="J571" s="3" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>24155000</v>
       </c>
       <c r="L571" s="5" t="n">
-        <v>26486</v>
+        <v>26515</v>
       </c>
       <c r="M571" s="3" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         </is>
       </c>
       <c r="E577" s="4" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F577" s="3" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>17000000</v>
       </c>
       <c r="I577" s="5" t="n">
-        <v>25915</v>
+        <v>25954</v>
       </c>
       <c r="J577" s="3" t="inlineStr">
         <is>
@@ -36388,7 +36388,7 @@
         <v>17000000</v>
       </c>
       <c r="L577" s="5" t="n">
-        <v>25915</v>
+        <v>25954</v>
       </c>
       <c r="M577" s="3" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         </is>
       </c>
       <c r="E580" s="4" t="n">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F580" s="3" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>28612000</v>
       </c>
       <c r="I580" s="5" t="n">
-        <v>31373</v>
+        <v>31407</v>
       </c>
       <c r="J580" s="3" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>28612000</v>
       </c>
       <c r="L580" s="5" t="n">
-        <v>31373</v>
+        <v>31407</v>
       </c>
       <c r="M580" s="3" t="inlineStr">
         <is>
@@ -36919,7 +36919,7 @@
         </is>
       </c>
       <c r="E586" s="4" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F586" s="3" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>16958000</v>
       </c>
       <c r="I586" s="5" t="n">
-        <v>25851</v>
+        <v>25890</v>
       </c>
       <c r="J586" s="3" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>16958000</v>
       </c>
       <c r="L586" s="5" t="n">
-        <v>25851</v>
+        <v>25890</v>
       </c>
       <c r="M586" s="3" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         </is>
       </c>
       <c r="E589" s="4" t="n">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F589" s="3" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>24094000</v>
       </c>
       <c r="I589" s="5" t="n">
-        <v>26419</v>
+        <v>26448</v>
       </c>
       <c r="J589" s="3" t="inlineStr">
         <is>
@@ -37132,7 +37132,7 @@
         <v>24094000</v>
       </c>
       <c r="L589" s="5" t="n">
-        <v>26419</v>
+        <v>26448</v>
       </c>
       <c r="M589" s="3" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         </is>
       </c>
       <c r="E595" s="4" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F595" s="3" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>16958000</v>
       </c>
       <c r="I595" s="5" t="n">
-        <v>25851</v>
+        <v>25890</v>
       </c>
       <c r="J595" s="3" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>16958000</v>
       </c>
       <c r="L595" s="5" t="n">
-        <v>25851</v>
+        <v>25890</v>
       </c>
       <c r="M595" s="3" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         </is>
       </c>
       <c r="E604" s="4" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F604" s="3" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>16873000</v>
       </c>
       <c r="I604" s="5" t="n">
-        <v>25721</v>
+        <v>25760</v>
       </c>
       <c r="J604" s="3" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>16873000</v>
       </c>
       <c r="L604" s="5" t="n">
-        <v>25721</v>
+        <v>25760</v>
       </c>
       <c r="M604" s="3" t="inlineStr">
         <is>
@@ -38807,9 +38807,9 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>G | 615呎 (2房)
+          <t>G | 614呎 (2房)
 $2513万
-$40,863/呎
+$40,930/呎
 (19年-07月-22日)</t>
         </is>
       </c>
@@ -38826,26 +38826,63 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 899呎 (3房)
+$2809万
+$31,244/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 614呎 (2房)
+$2371万
+$38,614/呎
+(19年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 617呎 (2房)
+$2265万
+$36,707/呎
+(19年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33&amp;35</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 3136呎 (4+房)
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 3221呎 (4+房)
 $17716万
-$56,491/呎
+$55,000/呎
 (21年-03月-23日)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 2334呎 (4+房)
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 2331呎 (4+房)
 $8578万
-$36,752/呎
+$36,800/呎
 (25年-12月-01日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 2375呎 (4+房)
 $11875万
@@ -38853,48 +38890,11 @@
 (19年-11月-20日)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
       <c r="E7" s="20" t="inlineStr"/>
       <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 899呎 (3房)
-$2809万
-$31,244/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 615呎 (2房)
-$2371万
-$38,551/呎
-(19年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>H | 617呎 (2房)
-$2265万
-$36,707/呎
-(19年-07月-09日)</t>
-        </is>
-      </c>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -38905,17 +38905,17 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 1485呎 (4+房)
+          <t>A | 1487呎 (4+房)
 $6687万
-$45,028/呎
+$44,968/呎
 (20年-10月-12日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 1201呎 (4+房)
+          <t>B | 1202呎 (4+房)
 $5058万
-$42,116/呎
+$42,081/呎
 (20年-06月-30日)</t>
         </is>
       </c>
@@ -38939,9 +38939,9 @@
       </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t>G | 615呎 (2房)
+          <t>G | 614呎 (2房)
 $2280万
-$37,068/呎
+$37,129/呎
 (19年-05月-24日)</t>
         </is>
       </c>
@@ -38970,17 +38970,17 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 1485呎 (4+房)
+          <t>A | 1487呎 (4+房)
 $6273万
-$42,242/呎
+$42,186/呎
 (19年-12月-20日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>B | 1201呎 (4+房)
+          <t>B | 1202呎 (4+房)
 $4817万
-$40,111/呎
+$40,077/呎
 (20年-06月-15日)</t>
         </is>
       </c>
@@ -39004,9 +39004,9 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>G | 615呎 (2房)
+          <t>G | 614呎 (2房)
 $2159万
-$35,111/呎
+$35,168/呎
 (19年-05月-06日)</t>
         </is>
       </c>
@@ -39035,9 +39035,9 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>A | 1485呎 (4+房)
+          <t>A | 1487呎 (4+房)
 $5870万
-$39,530/呎
+$39,477/呎
 (18年-07月-17日)</t>
         </is>
       </c>
@@ -39100,17 +39100,17 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 1485呎 (4+房)
+          <t>A | 1487呎 (4+房)
 $5104万
-$34,374/呎
+$34,328/呎
 (18年-06月-29日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>B | 1201呎 (4+房)
+          <t>B | 1202呎 (4+房)
 $3954万
-$32,925/呎
+$32,898/呎
 (18年-06月-29日)</t>
         </is>
       </c>
@@ -39173,9 +39173,9 @@
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>B | 1201呎 (4+房)
+          <t>B | 1202呎 (4+房)
 $3954万
-$32,925/呎
+$32,898/呎
 (18年-06月-29日)</t>
         </is>
       </c>
@@ -39199,9 +39199,9 @@
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t>G | 615呎 (2房)
+          <t>G | 614呎 (2房)
 $2076万
-$33,748/呎
+$33,803/呎
 (18年-08月-15日)</t>
         </is>
       </c>
@@ -39238,9 +39238,9 @@
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>B | 1201呎 (4+房)
+          <t>B | 1202呎 (4+房)
 $3933万
-$32,745/呎
+$32,718/呎
 (18年-07月-03日)</t>
         </is>
       </c>
@@ -39264,9 +39264,9 @@
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t>G | 615呎 (2房)
+          <t>G | 614呎 (2房)
 $2003万
-$32,574/呎
+$32,627/呎
 (18年-07月-31日)</t>
         </is>
       </c>
@@ -39295,9 +39295,9 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>A | 1485呎 (4+房)
+          <t>A | 1487呎 (4+房)
 $4812万
-$32,404/呎
+$32,360/呎
 (18年-07月-03日)</t>
         </is>
       </c>
@@ -39329,9 +39329,9 @@
       </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t>G | 615呎 (2房)
+          <t>G | 614呎 (2房)
 $1964万
-$31,935/呎
+$31,987/呎
 (18年-07月-27日)</t>
         </is>
       </c>
@@ -39463,9 +39463,9 @@
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>D | 781呎 (3房)
+          <t>D | 783呎 (3房)
 $2141万
-$27,408/呎
+$27,338/呎
 (18年-06月-28日)</t>
         </is>
       </c>
@@ -39621,9 +39621,9 @@
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>D | 781呎 (3房)
+          <t>D | 783呎 (3房)
 $2058万
-$26,346/呎
+$26,278/呎
 (18年-07月-03日)</t>
         </is>
       </c>
@@ -39700,9 +39700,9 @@
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
-          <t>D | 781呎 (3房)
+          <t>D | 783呎 (3房)
 $2037万
-$26,086/呎
+$26,019/呎
 (18年-07月-03日)</t>
         </is>
       </c>
@@ -39779,9 +39779,9 @@
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>D | 781呎 (3房)
+          <t>D | 783呎 (3房)
 $2017万
-$25,828/呎
+$25,762/呎
 (18年-07月-03日)</t>
         </is>
       </c>
@@ -39858,9 +39858,9 @@
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
-          <t>D | 781呎 (3房)
+          <t>D | 783呎 (3房)
 $2017万
-$25,828/呎
+$25,762/呎
 (18年-06月-29日)</t>
         </is>
       </c>
@@ -39937,9 +39937,9 @@
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>D | 781呎 (3房)
+          <t>D | 783呎 (3房)
 $1978万
-$25,321/呎
+$25,257/呎
 (18年-06月-28日)</t>
         </is>
       </c>
@@ -40016,9 +40016,9 @@
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
-          <t>D | 781呎 (3房)
+          <t>D | 783呎 (3房)
 $2325万
-$29,771/呎
+$29,695/呎
 (18年-06月-29日)</t>
         </is>
       </c>
@@ -40095,9 +40095,9 @@
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
-          <t>D | 781呎 (3房)
+          <t>D | 783呎 (3房)
 $2018万
-$25,845/呎
+$25,779/呎
 (18年-07月-03日)</t>
         </is>
       </c>
@@ -40253,9 +40253,9 @@
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>D | 781呎 (3房)
+          <t>D | 783呎 (3房)
 $1998万
-$25,589/呎
+$25,524/呎
 (18年-07月-04日)</t>
         </is>
       </c>
@@ -40332,9 +40332,9 @@
       </c>
       <c r="E27" s="21" t="inlineStr">
         <is>
-          <t>D | 781呎 (3房)
+          <t>D | 783呎 (3房)
 $2362万
-$30,237/呎
+$30,160/呎
 (18年-07月-04日)</t>
         </is>
       </c>
@@ -40411,9 +40411,9 @@
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>D | 781呎 (3房)
+          <t>D | 783呎 (3房)
 $1979万
-$25,335/呎
+$25,271/呎
 (18年-07月-04日)</t>
         </is>
       </c>
@@ -40490,9 +40490,9 @@
       </c>
       <c r="E29" s="21" t="inlineStr">
         <is>
-          <t>D | 781呎 (3房)
+          <t>D | 783呎 (3房)
 $1969万
-$25,209/呎
+$25,144/呎
 (18年-07月-04日)</t>
         </is>
       </c>
@@ -40569,9 +40569,9 @@
       </c>
       <c r="E30" s="21" t="inlineStr">
         <is>
-          <t>D | 781呎 (3房)
+          <t>D | 783呎 (3房)
 $1959万
-$25,085/呎
+$25,020/呎
 (18年-07月-04日)</t>
         </is>
       </c>
@@ -40881,10 +40881,46 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1014呎 (4+房)
+$4398万
+$43,370/呎
+(19年-10月-22日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 1048呎 (4+房)
+$4284万
+$40,874/呎
+(20年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 1075呎 (4+房)
+$3477万
+$32,347/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33&amp;35</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2058呎 (4+房)
 $10496万
@@ -40892,8 +40928,8 @@
 (20年-04月-01日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1856呎 (4+房)
 $9317万
@@ -40901,53 +40937,17 @@
 (22年-07月-21日)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>E | 2028呎 (4+房)
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 2027呎 (4+房)
 $10500万
-$51,774/呎
+$51,800/呎
 (21年-03月-10日)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1014呎 (4+房)
-$4398万
-$43,370/呎
-(19年-10月-22日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 1048呎 (4+房)
-$4284万
-$40,874/呎
-(20年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 1075呎 (4+房)
-$3477万
-$32,347/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -40991,9 +40991,9 @@
       </c>
       <c r="G8" s="21" t="inlineStr">
         <is>
-          <t>F | 1032呎 (4+房)
+          <t>F | 1033呎 (4+房)
 $4295万
-$41,614/呎
+$41,574/呎
 (20年-09月-08日)</t>
         </is>
       </c>
@@ -41048,9 +41048,9 @@
       </c>
       <c r="G9" s="21" t="inlineStr">
         <is>
-          <t>F | 1032呎 (4+房)
+          <t>F | 1033呎 (4+房)
 $4170万
-$40,402/呎
+$40,363/呎
 (20年-09月-02日)</t>
         </is>
       </c>
@@ -41219,9 +41219,9 @@
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
-          <t>F | 1032呎 (4+房)
+          <t>F | 1033呎 (4+房)
 $2821万
-$27,333/呎
+$27,307/呎
 (26年-01月-05日)</t>
         </is>
       </c>
@@ -41276,9 +41276,9 @@
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>F | 1032呎 (4+房)
+          <t>F | 1033呎 (4+房)
 $2765万
-$26,797/呎
+$26,771/呎
 (26年-01月-05日)</t>
         </is>
       </c>
@@ -41333,9 +41333,9 @@
       </c>
       <c r="G14" s="21" t="inlineStr">
         <is>
-          <t>F | 1032呎 (4+房)
+          <t>F | 1033呎 (4+房)
 $3769万
-$36,522/呎
+$36,487/呎
 (19年-09月-04日)</t>
         </is>
       </c>
@@ -41357,9 +41357,9 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>A | 805呎 (3房)
+          <t>A | 804呎 (3房)
 $2730万
-$33,913/呎
+$33,955/呎
 (18年-07月-04日)</t>
         </is>
       </c>
@@ -41389,25 +41389,25 @@
       </c>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t>E | 677呎 (2房)
+          <t>E | 678呎 (2房)
 $2099万
-$31,006/呎
+$30,960/呎
 (18年-08月-07日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>
-          <t>F | 837呎 (3房)
+          <t>F | 838呎 (3房)
 $2447万
-$29,233/呎
+$29,198/呎
 (18年-07月-05日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t>G | 908呎 (3房)
+          <t>G | 909呎 (3房)
 $2726万
-$30,028/呎
+$29,994/呎
 (18年-07月-05日)</t>
         </is>
       </c>
@@ -41428,9 +41428,9 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>A | 805呎 (3房)
+          <t>A | 804呎 (3房)
 $2650万
-$32,925/呎
+$32,966/呎
 (18年-07月-05日)</t>
         </is>
       </c>
@@ -41468,17 +41468,17 @@
       </c>
       <c r="G16" s="21" t="inlineStr">
         <is>
-          <t>F | 837呎 (3房)
+          <t>F | 838呎 (3房)
 $2411万
-$28,802/呎
+$28,767/呎
 (18年-07月-10日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
         <is>
-          <t>G | 908呎 (3房)
+          <t>G | 909呎 (3房)
 $2686万
-$29,584/呎
+$29,551/呎
 (18年-07月-03日)</t>
         </is>
       </c>
@@ -41499,9 +41499,9 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>A | 805呎 (3房)
+          <t>A | 804呎 (3房)
 $2573万
-$31,966/呎
+$32,006/呎
 (18年-07月-03日)</t>
         </is>
       </c>
@@ -41547,9 +41547,9 @@
       </c>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t>G | 908呎 (3房)
+          <t>G | 909呎 (3房)
 $2646万
-$29,146/呎
+$29,114/呎
 (18年-07月-03日)</t>
         </is>
       </c>
@@ -41570,9 +41570,9 @@
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>A | 805呎 (3房)
+          <t>A | 804呎 (3房)
 $2548万
-$31,650/呎
+$31,689/呎
 (18年-07月-10日)</t>
         </is>
       </c>
@@ -41681,9 +41681,9 @@
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>F | 837呎 (3房)
+          <t>F | 838呎 (3房)
 $2305万
-$27,542/呎
+$27,510/呎
 (18年-07月-06日)</t>
         </is>
       </c>
@@ -41760,9 +41760,9 @@
       </c>
       <c r="H20" s="21" t="inlineStr">
         <is>
-          <t>G | 908呎 (3房)
+          <t>G | 909呎 (3房)
 $2556万
-$28,151/呎
+$28,120/呎
 (18年-07月-05日)</t>
         </is>
       </c>
@@ -41815,9 +41815,9 @@
       </c>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t>E | 677呎 (2房)
+          <t>E | 678呎 (2房)
 $1884万
-$27,823/呎
+$27,782/呎
 (18年-08月-08日)</t>
         </is>
       </c>
@@ -41831,9 +41831,9 @@
       </c>
       <c r="H21" s="21" t="inlineStr">
         <is>
-          <t>G | 908呎 (3房)
+          <t>G | 909呎 (3房)
 $2556万
-$28,151/呎
+$28,120/呎
 (18年-07月-06日)</t>
         </is>
       </c>
@@ -41854,9 +41854,9 @@
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>A | 805呎 (3房)
+          <t>A | 804呎 (3房)
 $2449万
-$30,419/呎
+$30,456/呎
 (18年-07月-05日)</t>
         </is>
       </c>
@@ -41886,9 +41886,9 @@
       </c>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t>E | 677呎 (2房)
+          <t>E | 678呎 (2房)
 $1847万
-$27,278/呎
+$27,237/呎
 (18年-07月-27日)</t>
         </is>
       </c>
@@ -41902,9 +41902,9 @@
       </c>
       <c r="H22" s="21" t="inlineStr">
         <is>
-          <t>G | 908呎 (3房)
+          <t>G | 909呎 (3房)
 $2531万
-$27,872/呎
+$27,842/呎
 (18年-07月-09日)</t>
         </is>
       </c>
@@ -41925,9 +41925,9 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>A | 805呎 (3房)
+          <t>A | 804呎 (3房)
 $2424万
-$30,117/呎
+$30,154/呎
 (18年-07月-05日)</t>
         </is>
       </c>
@@ -42044,9 +42044,9 @@
       </c>
       <c r="H24" s="21" t="inlineStr">
         <is>
-          <t>G | 908呎 (3房)
+          <t>G | 909呎 (3房)
 $2506万
-$27,595/呎
+$27,564/呎
 (18年-07月-05日)</t>
         </is>
       </c>
@@ -42067,9 +42067,9 @@
       </c>
       <c r="B25" s="21" t="inlineStr">
         <is>
-          <t>A | 805呎 (3房)
+          <t>A | 804呎 (3房)
 $2377万
-$29,524/呎
+$29,561/呎
 (18年-07月-06日)</t>
         </is>
       </c>
@@ -42099,17 +42099,17 @@
       </c>
       <c r="F25" s="21" t="inlineStr">
         <is>
-          <t>E | 677呎 (2房)
+          <t>E | 678呎 (2房)
 $1810万
-$26,740/呎
+$26,701/呎
 (18年-07月-19日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>F | 837呎 (3房)
+          <t>F | 838呎 (3房)
 $2238万
-$26,732/呎
+$26,700/呎
 (18年-07月-09日)</t>
         </is>
       </c>
@@ -42170,9 +42170,9 @@
       </c>
       <c r="F26" s="21" t="inlineStr">
         <is>
-          <t>E | 677呎 (2房)
+          <t>E | 678呎 (2房)
 $1801万
-$26,606/呎
+$26,566/呎
 (18年-07月-16日)</t>
         </is>
       </c>
@@ -42241,9 +42241,9 @@
       </c>
       <c r="F27" s="21" t="inlineStr">
         <is>
-          <t>E | 677呎 (2房)
+          <t>E | 678呎 (2房)
 $1792万
-$26,474/呎
+$26,435/呎
 (18年-07月-16日)</t>
         </is>
       </c>
@@ -42257,9 +42257,9 @@
       </c>
       <c r="H27" s="21" t="inlineStr">
         <is>
-          <t>G | 908呎 (3房)
+          <t>G | 909呎 (3房)
 $2468万
-$27,185/呎
+$27,155/呎
 (18年-07月-04日)</t>
         </is>
       </c>
@@ -42280,9 +42280,9 @@
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>A | 805呎 (3房)
+          <t>A | 804呎 (3房)
 $2273万
-$28,236/呎
+$28,271/呎
 (18年-07月-09日)</t>
         </is>
       </c>
@@ -42351,9 +42351,9 @@
       </c>
       <c r="B29" s="21" t="inlineStr">
         <is>
-          <t>A | 805呎 (3房)
+          <t>A | 804呎 (3房)
 $2273万
-$28,236/呎
+$28,271/呎
 (18年-07月-10日)</t>
         </is>
       </c>
@@ -42383,17 +42383,17 @@
       </c>
       <c r="F29" s="21" t="inlineStr">
         <is>
-          <t>E | 677呎 (2房)
+          <t>E | 678呎 (2房)
 $1788万
-$26,408/呎
+$26,369/呎
 (18年-07月-16日)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
         <is>
-          <t>F | 837呎 (3房)
+          <t>F | 838呎 (3房)
 $2210万
-$26,400/呎
+$26,369/呎
 (18年-07月-10日)</t>
         </is>
       </c>
@@ -42462,17 +42462,17 @@
       </c>
       <c r="G30" s="21" t="inlineStr">
         <is>
-          <t>F | 837呎 (3房)
+          <t>F | 838呎 (3房)
 $2199万
-$26,269/呎
+$26,237/呎
 (18年-07月-04日)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
         <is>
-          <t>G | 908呎 (3房)
+          <t>G | 909呎 (3房)
 $2450万
-$26,982/呎
+$26,953/呎
 (18年-07月-10日)</t>
         </is>
       </c>
@@ -42493,9 +42493,9 @@
       </c>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t>A | 805呎 (3房)
+          <t>A | 804呎 (3房)
 $2239万
-$27,817/呎
+$27,852/呎
 (18年-07月-16日)</t>
         </is>
       </c>
@@ -42525,25 +42525,25 @@
       </c>
       <c r="F31" s="21" t="inlineStr">
         <is>
-          <t>E | 677呎 (2房)
+          <t>E | 678呎 (2房)
 $1774万
-$26,211/呎
+$26,173/呎
 (18年-07月-16日)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
         <is>
-          <t>F | 837呎 (3房)
+          <t>F | 838呎 (3房)
 $2193万
-$26,203/呎
+$26,172/呎
 (18年-07月-09日)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
         <is>
-          <t>G | 908呎 (3房)
+          <t>G | 909呎 (3房)
 $2444万
-$26,916/呎
+$26,887/呎
 (18年-07月-09日)</t>
         </is>
       </c>
@@ -42718,9 +42718,9 @@
       <c r="B5" s="20" t="inlineStr"/>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 662呎 (1房)
+          <t>B | 622呎 (1房)
 $3106万
-$46,920/呎
+$49,937/呎
 (19年-10月-22日)</t>
         </is>
       </c>
@@ -42737,9 +42737,9 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>G | 907呎 (3房)
+          <t>G | 908呎 (3房)
 $2897万
-$31,938/呎
+$31,903/呎
 (18年-07月-04日)</t>
         </is>
       </c>
@@ -42756,27 +42756,71 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 662呎 (1房)
+$2895万
+$43,731/呎
+(19年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 908呎 (3房)
+$2902万
+$31,961/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 908呎 (3房)
+$2840万
+$31,278/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 834呎 (3房)
+$2659万
+$31,880/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33&amp;35</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 2503呎 (4+房)
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 2502呎 (4+房)
 $12510万
-$49,980/呎
+$50,000/呎
 (23年-05月-22日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>C | 1624呎 (4+房)
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 1625呎 (4+房)
 $8206万
-$50,531/呎
+$50,500/呎
 (20年-03月-23日)</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 2282呎 (4+房)
 招标单位
@@ -42784,54 +42828,10 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 662呎 (1房)
-$2895万
-$43,731/呎
-(19年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
       <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 908呎 (3房)
-$2902万
-$31,961/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 908呎 (3房)
-$2840万
-$31,278/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>H | 834呎 (3房)
-$2659万
-$31,880/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -42842,25 +42842,25 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 1511呎 (4+房)
+          <t>A | 1512呎 (4+房)
 $6938万
-$45,919/呎
+$45,889/呎
 (19年-06月-26日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 616呎 (1房)
+          <t>B | 615呎 (1房)
 $2586万
-$41,982/呎
+$42,050/呎
 (19年-05月-23日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>C | 799呎 (3房)
+          <t>C | 798呎 (3房)
 $3169万
-$39,657/呎
+$39,707/呎
 (19年-02月-13日)</t>
         </is>
       </c>
@@ -42875,9 +42875,9 @@
       <c r="F8" s="20" t="inlineStr"/>
       <c r="G8" s="21" t="inlineStr">
         <is>
-          <t>F | 882呎 (3房)
+          <t>F | 881呎 (3房)
 $2621万
-$29,720/呎
+$29,754/呎
 (18年-06月-29日)</t>
         </is>
       </c>
@@ -42907,17 +42907,17 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 1536呎 (4+房)
+          <t>A | 1512呎 (4+房)
 $6689万
-$43,546/呎
+$44,237/呎
 (19年-11月-27日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>B | 616呎 (1房)
+          <t>B | 615呎 (1房)
 $2403万
-$39,006/呎
+$39,070/呎
 (18年-07月-17日)</t>
         </is>
       </c>
@@ -42940,9 +42940,9 @@
       <c r="F9" s="20" t="inlineStr"/>
       <c r="G9" s="21" t="inlineStr">
         <is>
-          <t>F | 882呎 (3房)
+          <t>F | 881呎 (3房)
 $2570万
-$29,138/呎
+$29,171/呎
 (18年-07月-03日)</t>
         </is>
       </c>
@@ -42980,17 +42980,17 @@
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>B | 616呎 (1房)
+          <t>B | 615呎 (1房)
 $2333万
-$37,870/呎
+$37,932/呎
 (19年-01月-07日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>C | 799呎 (3房)
+          <t>C | 798呎 (3房)
 $2794万
-$34,971/呎
+$35,015/呎
 (18年-07月-04日)</t>
         </is>
       </c>
@@ -43005,9 +43005,9 @@
       <c r="F10" s="20" t="inlineStr"/>
       <c r="G10" s="21" t="inlineStr">
         <is>
-          <t>F | 882呎 (3房)
+          <t>F | 881呎 (3房)
 $2520万
-$28,567/呎
+$28,599/呎
 (18年-07月-03日)</t>
         </is>
       </c>
@@ -43037,9 +43037,9 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 1536呎 (4+房)
+          <t>A | 1512呎 (4+房)
 $5496万
-$35,781/呎
+$36,349/呎
 (18年-07月-04日)</t>
         </is>
       </c>
@@ -43070,9 +43070,9 @@
       <c r="F11" s="20" t="inlineStr"/>
       <c r="G11" s="21" t="inlineStr">
         <is>
-          <t>F | 882呎 (3房)
+          <t>F | 881呎 (3房)
 $2470万
-$28,007/呎
+$28,039/呎
 (18年-07月-04日)</t>
         </is>
       </c>
@@ -43110,9 +43110,9 @@
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>B | 616呎 (1房)
+          <t>B | 615呎 (1房)
 $2287万
-$37,130/呎
+$37,190/呎
 (19年-01月-31日)</t>
         </is>
       </c>
@@ -43143,9 +43143,9 @@
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t>G | 907呎 (3房)
+          <t>G | 908呎 (3房)
 $2624万
-$28,928/呎
+$28,896/呎
 (18年-07月-04日)</t>
         </is>
       </c>
@@ -43167,25 +43167,25 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>A | 1537呎 (4+房)
+          <t>A | 1512呎 (4+房)
 $5792万
-$37,684/呎
+$38,307/呎
 (18年-07月-04日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>B | 616呎 (1房)
+          <t>B | 615呎 (1房)
 $2199万
-$35,701/呎
+$35,759/呎
 (18年-07月-31日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>C | 799呎 (3房)
+          <t>C | 798呎 (3房)
 $2744万
-$34,340/呎
+$34,383/呎
 (18年-07月-03日)</t>
         </is>
       </c>
@@ -43208,9 +43208,9 @@
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t>G | 907呎 (3房)
+          <t>G | 908呎 (3房)
 $2533万
-$27,923/呎
+$27,892/呎
 (18年-07月-03日)</t>
         </is>
       </c>
@@ -43232,17 +43232,17 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>A | 1511呎 (4+房)
+          <t>A | 1512呎 (4+房)
 $5820万
-$38,520/呎
+$38,494/呎
 (19年-06月-26日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>B | 616呎 (1房)
+          <t>B | 615呎 (1房)
 $2156万
-$35,000/呎
+$35,057/呎
 (18年-07月-17日)</t>
         </is>
       </c>
@@ -43297,9 +43297,9 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>A | 656呎 (1房)
+          <t>A | 655呎 (1房)
 $1953万
-$29,768/呎
+$29,814/呎
 (18年-07月-17日)</t>
         </is>
       </c>
@@ -43455,9 +43455,9 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>A | 656呎 (1房)
+          <t>A | 655呎 (1房)
 $1841万
-$28,061/呎
+$28,104/呎
 (18年-09月-27日)</t>
         </is>
       </c>
@@ -43503,9 +43503,9 @@
       </c>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t>G | 912呎 (3房)
+          <t>G | 911呎 (3房)
 $2371万
-$25,995/呎
+$26,023/呎
 (18年-06月-28日)</t>
         </is>
       </c>
@@ -43534,9 +43534,9 @@
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>A | 656呎 (1房)
+          <t>A | 655呎 (1房)
 $1822万
-$27,782/呎
+$27,824/呎
 (19年-03月-12日)</t>
         </is>
       </c>
@@ -43613,9 +43613,9 @@
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>A | 656呎 (1房)
+          <t>A | 655呎 (1房)
 $1804万
-$27,508/呎
+$27,550/呎
 (19年-03月-13日)</t>
         </is>
       </c>
@@ -43661,9 +43661,9 @@
       </c>
       <c r="H19" s="21" t="inlineStr">
         <is>
-          <t>G | 912呎 (3房)
+          <t>G | 911呎 (3房)
 $2301万
-$25,232/呎
+$25,260/呎
 (18年-06月-28日)</t>
         </is>
       </c>
@@ -43740,9 +43740,9 @@
       </c>
       <c r="H20" s="21" t="inlineStr">
         <is>
-          <t>G | 912呎 (3房)
+          <t>G | 911呎 (3房)
 $2411万
-$26,440/呎
+$26,469/呎
 (18年-07月-05日)</t>
         </is>
       </c>
@@ -43819,9 +43819,9 @@
       </c>
       <c r="H21" s="21" t="inlineStr">
         <is>
-          <t>G | 912呎 (3房)
+          <t>G | 911呎 (3房)
 $2411万
-$26,440/呎
+$26,469/呎
 (18年-07月-04日)</t>
         </is>
       </c>
@@ -43850,9 +43850,9 @@
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>A | 656呎 (1房)
+          <t>A | 655呎 (1房)
 $1752万
-$26,701/呎
+$26,742/呎
 (19年-03月-13日)</t>
         </is>
       </c>
@@ -43898,9 +43898,9 @@
       </c>
       <c r="H22" s="21" t="inlineStr">
         <is>
-          <t>G | 912呎 (3房)
+          <t>G | 911呎 (3房)
 $2287万
-$25,077/呎
+$25,104/呎
 (18年-07月-06日)</t>
         </is>
       </c>
@@ -43929,9 +43929,9 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>A | 656呎 (1房)
+          <t>A | 655呎 (1房)
 $1734万
-$26,438/呎
+$26,478/呎
 (18年-07月-24日)</t>
         </is>
       </c>
@@ -43977,9 +43977,9 @@
       </c>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t>G | 912呎 (3房)
+          <t>G | 911呎 (3房)
 $2440万
-$26,751/呎
+$26,780/呎
 (18年-07月-24日)</t>
         </is>
       </c>
@@ -44056,9 +44056,9 @@
       </c>
       <c r="H24" s="21" t="inlineStr">
         <is>
-          <t>G | 912呎 (3房)
+          <t>G | 911呎 (3房)
 $2452万
-$26,885/呎
+$26,914/呎
 (18年-07月-30日)</t>
         </is>
       </c>
@@ -44135,9 +44135,9 @@
       </c>
       <c r="H25" s="21" t="inlineStr">
         <is>
-          <t>G | 912呎 (3房)
+          <t>G | 911呎 (3房)
 $2440万
-$26,750/呎
+$26,779/呎
 (18年-07月-25日)</t>
         </is>
       </c>
@@ -44166,9 +44166,9 @@
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>A | 656呎 (1房)
+          <t>A | 655呎 (1房)
 $1708万
-$26,044/呎
+$26,084/呎
 (19年-02月-13日)</t>
         </is>
       </c>
@@ -44245,9 +44245,9 @@
       </c>
       <c r="B27" s="21" t="inlineStr">
         <is>
-          <t>A | 656呎 (1房)
+          <t>A | 655呎 (1房)
 $1700万
-$25,915/呎
+$25,954/呎
 (18年-08月-10日)</t>
         </is>
       </c>
@@ -44293,9 +44293,9 @@
       </c>
       <c r="H27" s="21" t="inlineStr">
         <is>
-          <t>G | 912呎 (3房)
+          <t>G | 911呎 (3房)
 $2416万
-$26,486/呎
+$26,515/呎
 (18年-07月-10日)</t>
         </is>
       </c>
@@ -44324,9 +44324,9 @@
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>A | 656呎 (1房)
+          <t>A | 655呎 (1房)
 $1696万
-$25,851/呎
+$25,890/呎
 (18年-07月-24日)</t>
         </is>
       </c>
@@ -44372,9 +44372,9 @@
       </c>
       <c r="H28" s="21" t="inlineStr">
         <is>
-          <t>G | 912呎 (3房)
+          <t>G | 911呎 (3房)
 $2861万
-$31,373/呎
+$31,407/呎
 (18年-07月-10日)</t>
         </is>
       </c>
@@ -44403,9 +44403,9 @@
       </c>
       <c r="B29" s="21" t="inlineStr">
         <is>
-          <t>A | 656呎 (1房)
+          <t>A | 655呎 (1房)
 $1696万
-$25,851/呎
+$25,890/呎
 (19年-01月-25日)</t>
         </is>
       </c>
@@ -44451,9 +44451,9 @@
       </c>
       <c r="H29" s="21" t="inlineStr">
         <is>
-          <t>G | 912呎 (3房)
+          <t>G | 911呎 (3房)
 $2409万
-$26,419/呎
+$26,448/呎
 (18年-07月-10日)</t>
         </is>
       </c>
@@ -44482,9 +44482,9 @@
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>A | 656呎 (1房)
+          <t>A | 655呎 (1房)
 $1687万
-$25,721/呎
+$25,760/呎
 (18年-12月-21日)</t>
         </is>
       </c>
